--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.71502385926907</v>
+        <v>1.741191377131224</v>
       </c>
       <c r="D2" t="n">
-        <v>11.75961052486227</v>
+        <v>1.910936710290118</v>
       </c>
       <c r="E2" t="n">
-        <v>3.984465918587893</v>
+        <v>0.6474757117705326</v>
       </c>
       <c r="F2" t="n">
-        <v>6.013739566245991</v>
+        <v>0.9772326795149735</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.746092022093281</v>
+        <v>0.4462399535901582</v>
       </c>
       <c r="D3" t="n">
-        <v>23.78708965735425</v>
+        <v>3.865402069320065</v>
       </c>
       <c r="E3" t="n">
-        <v>3.984465918587893</v>
+        <v>0.6474757117705326</v>
       </c>
       <c r="F3" t="n">
-        <v>6.013739566245991</v>
+        <v>0.9772326795149735</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
